--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="11_F32A27C7A1AC563A67AB634FA8BB63F59EA31876" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFDBE8A9-0E5F-4ED4-AB2E-262FD9EF8EDA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Was having presentation</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -573,10 +576,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2170,158 +2169,326 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="14">
+        <v>550</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>160</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>240</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>30</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>240</v>
+      </c>
+      <c r="G31" s="14">
+        <v>6</v>
+      </c>
+      <c r="H31" s="14">
+        <v>180</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="14">
+        <v>740</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>360</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>580</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>0</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>420</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>610</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>30</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>420</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>120</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>240</v>
+      </c>
+      <c r="F35" s="14">
+        <v>180</v>
+      </c>
+      <c r="G35" s="14">
+        <v>3</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>510</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>30</v>
+      </c>
+      <c r="E36" s="14">
+        <v>120</v>
+      </c>
+      <c r="F36" s="14">
+        <v>420</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>120</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6C533A6-58B1-4436-A5C7-DDD576054811}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t>Good</t>
-  </si>
-  <si>
-    <t>feeling good</t>
   </si>
   <si>
     <t>High</t>
@@ -235,12 +232,6 @@
     <t>Can't Attend classes but utilized time in other activities</t>
   </si>
   <si>
-    <t>Utilized the Sunday in other activities and hobbies</t>
-  </si>
-  <si>
-    <t>Attended family gathering on festival</t>
-  </si>
-  <si>
     <t>Practiced For CA</t>
   </si>
   <si>
@@ -248,9 +239,6 @@
   </si>
   <si>
     <t>Attended all classes today and feeling tired</t>
-  </si>
-  <si>
-    <t>Utilized my day well</t>
   </si>
   <si>
     <t>Medium</t>
@@ -263,9 +251,6 @@
   </si>
   <si>
     <t>Was having presentation</t>
-  </si>
-  <si>
-    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -576,6 +561,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -763,17 +752,17 @@
   <sheetData>
     <row r="1" spans="1:1" ht="22.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
@@ -781,12 +770,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
@@ -794,22 +783,22 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
@@ -817,17 +806,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
@@ -835,77 +824,77 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
@@ -913,17 +902,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
@@ -946,7 +935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N387"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1120,36 +1109,36 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B7" s="14">
-        <v>480</v>
+        <v>560</v>
       </c>
       <c r="C7" s="14">
         <v>60</v>
       </c>
       <c r="D7" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E7" s="14">
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="G7" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" s="14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I7" s="15">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="J7" s="15">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>26</v>
@@ -1158,115 +1147,115 @@
         <v>23</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B8" s="14">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C8" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D8" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E8" s="14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F8" s="14">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H8" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I8" s="15">
-        <v>1260</v>
+        <v>740</v>
       </c>
       <c r="J8" s="15">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B9" s="14">
-        <v>560</v>
+        <v>490</v>
       </c>
       <c r="C9" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D9" s="14">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E9" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F9" s="14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" s="14">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I9" s="15">
-        <v>1010</v>
+        <v>760</v>
       </c>
       <c r="J9" s="15">
-        <v>430</v>
+        <v>680</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B10" s="14">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="C10" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D10" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E10" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F10" s="14">
         <v>0</v>
@@ -1275,86 +1264,90 @@
         <v>0</v>
       </c>
       <c r="H10" s="14">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="I10" s="15">
-        <v>740</v>
+        <f t="shared" ref="I10:I61" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <v>1020</v>
       </c>
       <c r="J10" s="15">
-        <v>700</v>
+        <f t="shared" ref="J10:J61" si="1">IF(I10="","",1440-I10)</f>
+        <v>420</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B11" s="14">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
         <v>30</v>
       </c>
-      <c r="D11" s="14">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14">
-        <v>0</v>
-      </c>
       <c r="F11" s="14">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G11" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11" s="14">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="I11" s="15">
-        <v>760</v>
+        <f t="shared" si="0"/>
+        <v>1110</v>
       </c>
       <c r="J11" s="15">
-        <v>680</v>
+        <f t="shared" si="1"/>
+        <v>330</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="B12" s="14">
-        <v>630</v>
+        <v>500</v>
       </c>
       <c r="C12" s="14">
         <v>0</v>
       </c>
       <c r="D12" s="14">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E12" s="14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="F12" s="14">
         <v>0</v>
@@ -1363,90 +1356,90 @@
         <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" ref="I12:I75" si="0">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v>1130</v>
+        <f t="shared" si="0"/>
+        <v>1160</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" ref="J12:J75" si="1">IF(I12="","",1440-I12)</f>
-        <v>310</v>
+        <f t="shared" si="1"/>
+        <v>280</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="M12" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="B13" s="14">
-        <v>560</v>
+        <v>620</v>
       </c>
       <c r="C13" s="14">
         <v>0</v>
       </c>
       <c r="D13" s="14">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E13" s="14">
         <v>60</v>
       </c>
       <c r="F13" s="14">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1160</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B14" s="14">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C14" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D14" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E14" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F14" s="14">
         <v>0</v>
@@ -1459,31 +1452,31 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="B15" s="14">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="C15" s="14">
         <v>0</v>
@@ -1492,7 +1485,7 @@
         <v>60</v>
       </c>
       <c r="E15" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14">
         <v>420</v>
@@ -1501,994 +1494,682 @@
         <v>7</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1190</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="B16" s="14">
-        <v>740</v>
+        <v>480</v>
       </c>
       <c r="C16" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
         <v>0</v>
       </c>
       <c r="E16" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
         <v>240</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
-      <c r="H16" s="14">
-        <v>120</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B17" s="14">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C17" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F17" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1140</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>300</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46263</v>
+        <v>46272</v>
       </c>
       <c r="B18" s="14">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="C18" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D18" s="14">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="E18" s="14">
         <v>120</v>
       </c>
       <c r="F18" s="14">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G18" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1220</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M18" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46264</v>
+        <v>46273</v>
       </c>
       <c r="B19" s="14">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="C19" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E19" s="14">
         <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G19" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1150</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>64</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="B20" s="14">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
         <v>120</v>
-      </c>
-      <c r="D20" s="14">
-        <v>60</v>
       </c>
       <c r="E20" s="14">
         <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1240</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46266</v>
+        <v>46281</v>
       </c>
       <c r="B21" s="14">
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="C21" s="14">
         <v>0</v>
       </c>
       <c r="D21" s="14">
+        <v>30</v>
+      </c>
+      <c r="E21" s="14">
         <v>120</v>
       </c>
-      <c r="E21" s="14">
-        <v>0</v>
-      </c>
       <c r="F21" s="14">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G21" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H21" s="14">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46267</v>
+        <v>46282</v>
       </c>
       <c r="B22" s="14">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="C22" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D22" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E22" s="14">
         <v>60</v>
       </c>
       <c r="F22" s="14">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1130</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46268</v>
+        <v>46283</v>
       </c>
       <c r="B23" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
         <v>30</v>
       </c>
-      <c r="D23" s="14">
+      <c r="E23" s="14">
         <v>0</v>
       </c>
-      <c r="E23" s="14">
-        <v>120</v>
-      </c>
       <c r="F23" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
         <v>240</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1050</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
-        <v>46269</v>
-      </c>
-      <c r="B24" s="14">
-        <v>510</v>
-      </c>
-      <c r="C24" s="14">
-        <v>60</v>
-      </c>
-      <c r="D24" s="14">
-        <v>30</v>
-      </c>
-      <c r="E24" s="14">
-        <v>120</v>
-      </c>
-      <c r="F24" s="14">
-        <v>300</v>
-      </c>
-      <c r="G24" s="14">
-        <v>5</v>
-      </c>
-      <c r="H24" s="14">
-        <v>120</v>
-      </c>
-      <c r="I24" s="15">
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1140</v>
-      </c>
-      <c r="J24" s="15">
+        <v/>
+      </c>
+      <c r="J24" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>74</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13">
-        <v>46270</v>
-      </c>
-      <c r="B25" s="14">
-        <v>610</v>
-      </c>
-      <c r="C25" s="14">
-        <v>60</v>
-      </c>
-      <c r="D25" s="14">
-        <v>120</v>
-      </c>
-      <c r="E25" s="14">
-        <v>30</v>
-      </c>
-      <c r="F25" s="14">
-        <v>0</v>
-      </c>
-      <c r="G25" s="14">
-        <v>0</v>
-      </c>
-      <c r="H25" s="14">
-        <v>240</v>
-      </c>
-      <c r="I25" s="15">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1060</v>
-      </c>
-      <c r="J25" s="15">
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>380</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>75</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
-        <v>46271</v>
-      </c>
-      <c r="B26" s="14">
-        <v>560</v>
-      </c>
-      <c r="C26" s="14">
-        <v>60</v>
-      </c>
-      <c r="D26" s="14">
-        <v>120</v>
-      </c>
-      <c r="E26" s="14">
-        <v>30</v>
-      </c>
-      <c r="F26" s="14">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>0</v>
-      </c>
-      <c r="H26" s="14">
-        <v>360</v>
-      </c>
-      <c r="I26" s="15">
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1130</v>
-      </c>
-      <c r="J26" s="15">
+        <v/>
+      </c>
+      <c r="J26" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>310</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>75</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
-        <v>46272</v>
-      </c>
-      <c r="B27" s="14">
-        <v>470</v>
-      </c>
-      <c r="C27" s="14">
-        <v>60</v>
-      </c>
-      <c r="D27" s="14">
-        <v>30</v>
-      </c>
-      <c r="E27" s="14">
-        <v>120</v>
-      </c>
-      <c r="F27" s="14">
-        <v>420</v>
-      </c>
-      <c r="G27" s="14">
-        <v>7</v>
-      </c>
-      <c r="H27" s="14">
-        <v>120</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1220</v>
-      </c>
-      <c r="J27" s="15">
+        <v/>
+      </c>
+      <c r="J27" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>220</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>46273</v>
-      </c>
-      <c r="B28" s="14">
-        <v>580</v>
-      </c>
-      <c r="C28" s="14">
-        <v>30</v>
-      </c>
-      <c r="D28" s="14">
-        <v>180</v>
-      </c>
-      <c r="E28" s="14">
-        <v>60</v>
-      </c>
-      <c r="F28" s="14">
-        <v>180</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="14">
-        <v>120</v>
-      </c>
-      <c r="I28" s="15">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1150</v>
-      </c>
-      <c r="J28" s="15">
+        <v/>
+      </c>
+      <c r="J28" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>290</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>76</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
-        <v>46274</v>
-      </c>
-      <c r="B29" s="14">
-        <v>460</v>
-      </c>
-      <c r="C29" s="14">
-        <v>60</v>
-      </c>
-      <c r="D29" s="14">
-        <v>120</v>
-      </c>
-      <c r="E29" s="14">
-        <v>60</v>
-      </c>
-      <c r="F29" s="14">
-        <v>420</v>
-      </c>
-      <c r="G29" s="14">
-        <v>7</v>
-      </c>
-      <c r="H29" s="14">
-        <v>120</v>
-      </c>
-      <c r="I29" s="15">
+      <c r="A29" s="13"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1240</v>
-      </c>
-      <c r="J29" s="15">
+        <v/>
+      </c>
+      <c r="J29" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
-        <v>46275</v>
-      </c>
-      <c r="B30" s="14">
-        <v>550</v>
-      </c>
-      <c r="C30" s="14">
-        <v>0</v>
-      </c>
-      <c r="D30" s="14">
-        <v>120</v>
-      </c>
-      <c r="E30" s="14">
-        <v>60</v>
-      </c>
-      <c r="F30" s="14">
-        <v>160</v>
-      </c>
-      <c r="G30" s="14">
-        <v>4</v>
-      </c>
-      <c r="H30" s="14">
-        <v>240</v>
-      </c>
-      <c r="I30" s="15">
+      <c r="A30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1130</v>
-      </c>
-      <c r="J30" s="15">
+        <v/>
+      </c>
+      <c r="J30" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>310</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>69</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
-        <v>46276</v>
-      </c>
-      <c r="B31" s="14">
-        <v>480</v>
-      </c>
-      <c r="C31" s="14">
-        <v>0</v>
-      </c>
-      <c r="D31" s="14">
-        <v>30</v>
-      </c>
-      <c r="E31" s="14">
-        <v>60</v>
-      </c>
-      <c r="F31" s="14">
-        <v>240</v>
-      </c>
-      <c r="G31" s="14">
-        <v>6</v>
-      </c>
-      <c r="H31" s="14">
-        <v>180</v>
-      </c>
-      <c r="I31" s="15">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>990</v>
-      </c>
-      <c r="J31" s="15">
+        <v/>
+      </c>
+      <c r="J31" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>74</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
-        <v>46277</v>
-      </c>
-      <c r="B32" s="14">
-        <v>740</v>
-      </c>
-      <c r="C32" s="14">
-        <v>60</v>
-      </c>
-      <c r="D32" s="14">
-        <v>120</v>
-      </c>
-      <c r="E32" s="14">
-        <v>120</v>
-      </c>
-      <c r="F32" s="14">
-        <v>0</v>
-      </c>
-      <c r="G32" s="14">
-        <v>0</v>
-      </c>
-      <c r="H32" s="14">
-        <v>360</v>
-      </c>
-      <c r="I32" s="15">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1400</v>
-      </c>
-      <c r="J32" s="15">
+        <v/>
+      </c>
+      <c r="J32" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>75</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
-        <v>46278</v>
-      </c>
-      <c r="B33" s="14">
-        <v>580</v>
-      </c>
-      <c r="C33" s="14">
-        <v>60</v>
-      </c>
-      <c r="D33" s="14">
-        <v>0</v>
-      </c>
-      <c r="E33" s="14">
-        <v>120</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14">
-        <v>420</v>
-      </c>
-      <c r="I33" s="15">
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="J33" s="15">
+        <v/>
+      </c>
+      <c r="J33" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="K33" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L33" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>75</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
-        <v>46279</v>
-      </c>
-      <c r="B34" s="14">
-        <v>610</v>
-      </c>
-      <c r="C34" s="14">
-        <v>60</v>
-      </c>
-      <c r="D34" s="14">
-        <v>30</v>
-      </c>
-      <c r="E34" s="14">
-        <v>60</v>
-      </c>
-      <c r="F34" s="14">
-        <v>420</v>
-      </c>
-      <c r="G34" s="14">
-        <v>7</v>
-      </c>
-      <c r="H34" s="14">
-        <v>120</v>
-      </c>
-      <c r="I34" s="15">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1300</v>
-      </c>
-      <c r="J34" s="15">
+        <v/>
+      </c>
+      <c r="J34" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>140</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13">
-        <v>46280</v>
-      </c>
-      <c r="B35" s="14">
-        <v>480</v>
-      </c>
-      <c r="C35" s="14">
-        <v>30</v>
-      </c>
-      <c r="D35" s="14">
-        <v>120</v>
-      </c>
-      <c r="E35" s="14">
-        <v>240</v>
-      </c>
-      <c r="F35" s="14">
-        <v>180</v>
-      </c>
-      <c r="G35" s="14">
-        <v>3</v>
-      </c>
-      <c r="H35" s="14">
-        <v>180</v>
-      </c>
-      <c r="I35" s="15">
+      <c r="A35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1230</v>
-      </c>
-      <c r="J35" s="15">
+        <v/>
+      </c>
+      <c r="J35" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="M35" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>74</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13">
-        <v>46281</v>
-      </c>
-      <c r="B36" s="14">
-        <v>510</v>
-      </c>
-      <c r="C36" s="14">
-        <v>0</v>
-      </c>
-      <c r="D36" s="14">
-        <v>30</v>
-      </c>
-      <c r="E36" s="14">
-        <v>120</v>
-      </c>
-      <c r="F36" s="14">
-        <v>420</v>
-      </c>
-      <c r="G36" s="14">
-        <v>7</v>
-      </c>
-      <c r="H36" s="14">
-        <v>120</v>
-      </c>
-      <c r="I36" s="15">
+      <c r="A36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-      <c r="J36" s="15">
+        <v/>
+      </c>
+      <c r="J36" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="N36" s="17" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
@@ -3050,11 +2731,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I62:I125" si="2">IF(SUM(B62:F62,H62)=0,"",SUM(B62:F62,H62))</f>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J62:J125" si="3">IF(I62="","",1440-I62)</f>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -3072,11 +2753,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -3094,11 +2775,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -3116,11 +2797,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -3138,11 +2819,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -3160,11 +2841,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -3182,11 +2863,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3204,11 +2885,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3226,11 +2907,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3248,11 +2929,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3270,11 +2951,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3292,11 +2973,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3314,11 +2995,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3336,11 +3017,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3358,11 +3039,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" ref="I76:I139" si="2">IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" ref="J76:J139" si="3">IF(I76="","",1440-I76)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -4458,11 +4139,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I126:I189" si="4">IF(SUM(B126:F126,H126)=0,"",SUM(B126:F126,H126))</f>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J126:J189" si="5">IF(I126="","",1440-I126)</f>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4480,11 +4161,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4502,11 +4183,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4524,11 +4205,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4546,11 +4227,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4568,11 +4249,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4590,11 +4271,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4612,11 +4293,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4634,11 +4315,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4656,11 +4337,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4678,11 +4359,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4700,11 +4381,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4722,11 +4403,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4744,11 +4425,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4766,11 +4447,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" ref="I140:I203" si="4">IF(SUM(B140:F140,H140)=0,"",SUM(B140:F140,H140))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" ref="J140:J203" si="5">IF(I140="","",1440-I140)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5866,11 +5547,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I190:I253" si="6">IF(SUM(B190:F190,H190)=0,"",SUM(B190:F190,H190))</f>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J190:J253" si="7">IF(I190="","",1440-I190)</f>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5888,11 +5569,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5910,11 +5591,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5932,11 +5613,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5954,11 +5635,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5976,11 +5657,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5998,11 +5679,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6020,11 +5701,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6042,11 +5723,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6064,11 +5745,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6086,11 +5767,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6108,11 +5789,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6130,11 +5811,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6152,11 +5833,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6174,11 +5855,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" ref="I204:I267" si="6">IF(SUM(B204:F204,H204)=0,"",SUM(B204:F204,H204))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" ref="J204:J267" si="7">IF(I204="","",1440-I204)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -7274,11 +6955,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I254:I317" si="8">IF(SUM(B254:F254,H254)=0,"",SUM(B254:F254,H254))</f>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J254:J317" si="9">IF(I254="","",1440-I254)</f>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7296,11 +6977,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7318,11 +6999,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7340,11 +7021,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7362,11 +7043,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7384,11 +7065,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7406,11 +7087,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7428,11 +7109,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7450,11 +7131,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7472,11 +7153,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7494,11 +7175,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7516,11 +7197,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7538,11 +7219,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7560,11 +7241,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7582,11 +7263,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" ref="I268:I331" si="8">IF(SUM(B268:F268,H268)=0,"",SUM(B268:F268,H268))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" ref="J268:J331" si="9">IF(I268="","",1440-I268)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8682,11 +8363,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I318:I381" si="10">IF(SUM(B318:F318,H318)=0,"",SUM(B318:F318,H318))</f>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J318:J381" si="11">IF(I318="","",1440-I318)</f>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8704,11 +8385,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8726,11 +8407,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8748,11 +8429,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8770,11 +8451,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8792,11 +8473,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8814,11 +8495,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8836,11 +8517,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8858,11 +8539,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8880,11 +8561,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8902,11 +8583,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8924,11 +8605,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8946,11 +8627,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8968,11 +8649,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8990,11 +8671,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" ref="I332:I395" si="10">IF(SUM(B332:F332,H332)=0,"",SUM(B332:F332,H332))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" ref="J332:J395" si="11">IF(I332="","",1440-I332)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -10090,11 +9771,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I382:I387" si="12">IF(SUM(B382:F382,H382)=0,"",SUM(B382:F382,H382))</f>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J382:J387" si="13">IF(I382="","",1440-I382)</f>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10112,11 +9793,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10134,11 +9815,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10156,11 +9837,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10178,11 +9859,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10200,325 +9881,17 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
       <c r="L387" s="16"/>
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A388" s="13"/>
-      <c r="B388" s="14"/>
-      <c r="C388" s="14"/>
-      <c r="D388" s="14"/>
-      <c r="E388" s="14"/>
-      <c r="F388" s="14"/>
-      <c r="G388" s="14"/>
-      <c r="H388" s="14"/>
-      <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K388" s="16"/>
-      <c r="L388" s="16"/>
-      <c r="M388" s="16"/>
-      <c r="N388" s="17"/>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A389" s="13"/>
-      <c r="B389" s="14"/>
-      <c r="C389" s="14"/>
-      <c r="D389" s="14"/>
-      <c r="E389" s="14"/>
-      <c r="F389" s="14"/>
-      <c r="G389" s="14"/>
-      <c r="H389" s="14"/>
-      <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K389" s="16"/>
-      <c r="L389" s="16"/>
-      <c r="M389" s="16"/>
-      <c r="N389" s="17"/>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A390" s="13"/>
-      <c r="B390" s="14"/>
-      <c r="C390" s="14"/>
-      <c r="D390" s="14"/>
-      <c r="E390" s="14"/>
-      <c r="F390" s="14"/>
-      <c r="G390" s="14"/>
-      <c r="H390" s="14"/>
-      <c r="I390" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J390" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K390" s="16"/>
-      <c r="L390" s="16"/>
-      <c r="M390" s="16"/>
-      <c r="N390" s="17"/>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A391" s="13"/>
-      <c r="B391" s="14"/>
-      <c r="C391" s="14"/>
-      <c r="D391" s="14"/>
-      <c r="E391" s="14"/>
-      <c r="F391" s="14"/>
-      <c r="G391" s="14"/>
-      <c r="H391" s="14"/>
-      <c r="I391" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J391" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K391" s="16"/>
-      <c r="L391" s="16"/>
-      <c r="M391" s="16"/>
-      <c r="N391" s="17"/>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A392" s="13"/>
-      <c r="B392" s="14"/>
-      <c r="C392" s="14"/>
-      <c r="D392" s="14"/>
-      <c r="E392" s="14"/>
-      <c r="F392" s="14"/>
-      <c r="G392" s="14"/>
-      <c r="H392" s="14"/>
-      <c r="I392" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J392" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K392" s="16"/>
-      <c r="L392" s="16"/>
-      <c r="M392" s="16"/>
-      <c r="N392" s="17"/>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A393" s="13"/>
-      <c r="B393" s="14"/>
-      <c r="C393" s="14"/>
-      <c r="D393" s="14"/>
-      <c r="E393" s="14"/>
-      <c r="F393" s="14"/>
-      <c r="G393" s="14"/>
-      <c r="H393" s="14"/>
-      <c r="I393" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J393" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K393" s="16"/>
-      <c r="L393" s="16"/>
-      <c r="M393" s="16"/>
-      <c r="N393" s="17"/>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A394" s="13"/>
-      <c r="B394" s="14"/>
-      <c r="C394" s="14"/>
-      <c r="D394" s="14"/>
-      <c r="E394" s="14"/>
-      <c r="F394" s="14"/>
-      <c r="G394" s="14"/>
-      <c r="H394" s="14"/>
-      <c r="I394" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J394" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K394" s="16"/>
-      <c r="L394" s="16"/>
-      <c r="M394" s="16"/>
-      <c r="N394" s="17"/>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A395" s="13"/>
-      <c r="B395" s="14"/>
-      <c r="C395" s="14"/>
-      <c r="D395" s="14"/>
-      <c r="E395" s="14"/>
-      <c r="F395" s="14"/>
-      <c r="G395" s="14"/>
-      <c r="H395" s="14"/>
-      <c r="I395" s="15" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J395" s="15" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K395" s="16"/>
-      <c r="L395" s="16"/>
-      <c r="M395" s="16"/>
-      <c r="N395" s="17"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A396" s="13"/>
-      <c r="B396" s="14"/>
-      <c r="C396" s="14"/>
-      <c r="D396" s="14"/>
-      <c r="E396" s="14"/>
-      <c r="F396" s="14"/>
-      <c r="G396" s="14"/>
-      <c r="H396" s="14"/>
-      <c r="I396" s="15" t="str">
-        <f t="shared" ref="I396:I401" si="12">IF(SUM(B396:F396,H396)=0,"",SUM(B396:F396,H396))</f>
-        <v/>
-      </c>
-      <c r="J396" s="15" t="str">
-        <f t="shared" ref="J396:J401" si="13">IF(I396="","",1440-I396)</f>
-        <v/>
-      </c>
-      <c r="K396" s="16"/>
-      <c r="L396" s="16"/>
-      <c r="M396" s="16"/>
-      <c r="N396" s="17"/>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A397" s="13"/>
-      <c r="B397" s="14"/>
-      <c r="C397" s="14"/>
-      <c r="D397" s="14"/>
-      <c r="E397" s="14"/>
-      <c r="F397" s="14"/>
-      <c r="G397" s="14"/>
-      <c r="H397" s="14"/>
-      <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K397" s="16"/>
-      <c r="L397" s="16"/>
-      <c r="M397" s="16"/>
-      <c r="N397" s="17"/>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="13"/>
-      <c r="B398" s="14"/>
-      <c r="C398" s="14"/>
-      <c r="D398" s="14"/>
-      <c r="E398" s="14"/>
-      <c r="F398" s="14"/>
-      <c r="G398" s="14"/>
-      <c r="H398" s="14"/>
-      <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="16"/>
-      <c r="L398" s="16"/>
-      <c r="M398" s="16"/>
-      <c r="N398" s="17"/>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="13"/>
-      <c r="B399" s="14"/>
-      <c r="C399" s="14"/>
-      <c r="D399" s="14"/>
-      <c r="E399" s="14"/>
-      <c r="F399" s="14"/>
-      <c r="G399" s="14"/>
-      <c r="H399" s="14"/>
-      <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="16"/>
-      <c r="L399" s="16"/>
-      <c r="M399" s="16"/>
-      <c r="N399" s="17"/>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10529,21 +9902,21 @@
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J387">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K387" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L387" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M387" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6C533A6-58B1-4436-A5C7-DDD576054811}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF4B487-1880-43EF-B7BB-759DBBA2EA45}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Was having presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked on my assignment </t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1508,7 @@
         <v>250</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>64</v>
@@ -1735,7 +1738,7 @@
         <v>200</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>63</v>
@@ -1886,26 +1889,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>120</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>360</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF4B487-1880-43EF-B7BB-759DBBA2EA45}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F4FE2B9-BF9B-4F84-968E-8180F898E1B7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t xml:space="preserve">Worked on my assignment </t>
+  </si>
+  <si>
+    <t>Worked on my assignment and ca</t>
   </si>
 </sst>
 </file>
@@ -1934,27 +1937,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B25" s="14">
+        <v>630</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F4FE2B9-BF9B-4F84-968E-8180F898E1B7}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C0C79FB-0806-4F8B-A57A-AFD6DCE16D31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Worked on my assignment and ca</t>
+  </si>
+  <si>
+    <t>Attended all classes felt a bit tired</t>
   </si>
 </sst>
 </file>
@@ -1983,27 +1986,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B26" s="14">
+        <v>510</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>360</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>210</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C0C79FB-0806-4F8B-A57A-AFD6DCE16D31}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C019383C-A19E-4D02-AA7A-00AD184FC22E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -235,9 +235,6 @@
     <t>Practiced For CA</t>
   </si>
   <si>
-    <t>Stressed</t>
-  </si>
-  <si>
     <t>Attended all classes today and feeling tired</t>
   </si>
   <si>
@@ -260,6 +257,15 @@
   </si>
   <si>
     <t>Attended all classes felt a bit tired</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Worked on assignment</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1115,7 @@
         <v>23</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>24</v>
@@ -1150,10 +1156,10 @@
         <v>430</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>27</v>
@@ -1170,7 +1176,7 @@
         <v>560</v>
       </c>
       <c r="C8" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D8" s="14">
         <v>0</v>
@@ -1194,10 +1200,10 @@
         <v>700</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>27</v>
@@ -1214,7 +1220,7 @@
         <v>490</v>
       </c>
       <c r="C9" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D9" s="14">
         <v>0</v>
@@ -1241,7 +1247,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>27</v>
@@ -1258,7 +1264,7 @@
         <v>420</v>
       </c>
       <c r="C10" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D10" s="14">
         <v>60</v>
@@ -1277,17 +1283,17 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" ref="I10:I61" si="0">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v>1020</v>
+        <v>1050</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" ref="J10:J61" si="1">IF(I10="","",1440-I10)</f>
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>62</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>27</v>
@@ -1333,13 +1339,13 @@
         <v>24</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="M11" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1350,7 +1356,7 @@
         <v>500</v>
       </c>
       <c r="C12" s="14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D12" s="14">
         <v>240</v>
@@ -1369,11 +1375,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1250</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>62</v>
@@ -1396,7 +1402,7 @@
         <v>620</v>
       </c>
       <c r="C13" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D13" s="14">
         <v>300</v>
@@ -1415,11 +1421,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1280</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>62</v>
@@ -1442,7 +1448,7 @@
         <v>450</v>
       </c>
       <c r="C14" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D14" s="14">
         <v>120</v>
@@ -1461,17 +1467,17 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1170</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>62</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>27</v>
@@ -1563,13 +1569,13 @@
         <v>26</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1580,7 +1586,7 @@
         <v>510</v>
       </c>
       <c r="C17" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
         <v>30</v>
@@ -1599,23 +1605,23 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1110</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1626,7 +1632,7 @@
         <v>470</v>
       </c>
       <c r="C18" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D18" s="14">
         <v>30</v>
@@ -1645,17 +1651,17 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1160</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>24</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>24</v>
@@ -1672,7 +1678,7 @@
         <v>580</v>
       </c>
       <c r="C19" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D19" s="14">
         <v>180</v>
@@ -1691,23 +1697,23 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>1180</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1718,7 +1724,7 @@
         <v>460</v>
       </c>
       <c r="C20" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D20" s="14">
         <v>120</v>
@@ -1737,17 +1743,17 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>1180</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>24</v>
@@ -1790,10 +1796,10 @@
         <v>240</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M21" s="16" t="s">
         <v>24</v>
@@ -1836,16 +1842,16 @@
         <v>310</v>
       </c>
       <c r="K22" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="M22" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1885,7 +1891,7 @@
         <v>23</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>24</v>
@@ -1931,13 +1937,13 @@
         <v>62</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1948,7 +1954,7 @@
         <v>630</v>
       </c>
       <c r="C25" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D25" s="14">
         <v>120</v>
@@ -1967,23 +1973,23 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>62</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>27</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2023,36 +2029,60 @@
         <v>26</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>24</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B27" s="14">
+        <v>210</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>120</v>
+      </c>
+      <c r="F27" s="14">
+        <v>180</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
+        <v>240</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C019383C-A19E-4D02-AA7A-00AD184FC22E}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6562CEC-604E-46EA-AA62-969C15F77376}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -2085,26 +2085,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B28" s="14">
+        <v>540</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>30</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>360</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>180</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6562CEC-604E-46EA-AA62-969C15F77376}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83CB09A7-17DF-4FAE-B889-FDFF394B7EE7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1147,7 +1147,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="14">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="I7" s="15">
         <v>1010</v>
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="14">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="I8" s="15">
         <v>740</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="14">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="I9" s="15">
         <v>760</v>
@@ -1417,15 +1417,15 @@
         <v>0</v>
       </c>
       <c r="H13" s="14">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1380</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>62</v>
@@ -1477,7 +1477,7 @@
         <v>62</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>27</v>
@@ -1509,21 +1509,21 @@
         <v>7</v>
       </c>
       <c r="H15" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1130</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>24</v>
@@ -1569,7 +1569,7 @@
         <v>26</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>24</v>
@@ -1601,21 +1601,21 @@
         <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1170</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>24</v>
@@ -1693,21 +1693,21 @@
         <v>3</v>
       </c>
       <c r="H19" s="14">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1180</v>
+        <v>1420</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>62</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>27</v>
@@ -1753,7 +1753,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>24</v>
@@ -1831,21 +1831,21 @@
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1250</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>68</v>
@@ -1877,21 +1877,21 @@
         <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>990</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>24</v>
@@ -1937,7 +1937,7 @@
         <v>62</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>27</v>
@@ -2015,21 +2015,21 @@
         <v>6</v>
       </c>
       <c r="H26" s="14">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1230</v>
+        <v>1050</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>24</v>
@@ -2061,21 +2061,21 @@
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>450</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>24</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>68</v>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83CB09A7-17DF-4FAE-B889-FDFF394B7EE7}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{481DB184-25B1-4A25-A27C-4B3846816B86}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="78">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -1112,7 +1112,7 @@
         <v>710</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>75</v>
@@ -1244,7 +1244,7 @@
         <v>680</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>75</v>
@@ -1290,7 +1290,7 @@
         <v>390</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>76</v>
@@ -1474,7 +1474,7 @@
         <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>64</v>
@@ -1520,7 +1520,7 @@
         <v>310</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>23</v>
@@ -1612,7 +1612,7 @@
         <v>270</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>64</v>
@@ -1658,7 +1658,7 @@
         <v>280</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>23</v>
@@ -1750,7 +1750,7 @@
         <v>260</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>64</v>
@@ -1842,7 +1842,7 @@
         <v>190</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>63</v>
@@ -1888,7 +1888,7 @@
         <v>450</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>75</v>
@@ -1934,7 +1934,7 @@
         <v>360</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="L24" s="16" t="s">
         <v>76</v>
@@ -2131,25 +2131,47 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B29" s="14">
+        <v>520</v>
+      </c>
+      <c r="C29" s="14">
+        <v>120</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>180</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>300</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{481DB184-25B1-4A25-A27C-4B3846816B86}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E87F6479-601C-40A9-83AD-6E25167A67CF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>Worked on assignment</t>
+  </si>
+  <si>
+    <t>Prepared for CA</t>
+  </si>
+  <si>
+    <t>Attended family Gathering</t>
   </si>
 </sst>
 </file>
@@ -2172,29 +2178,55 @@
       <c r="M29" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="N29" s="17"/>
+      <c r="N29" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B30" s="14">
+        <v>540</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>30</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>300</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>180</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E87F6479-601C-40A9-83AD-6E25167A67CF}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1619DEFF-23F1-492C-B0BF-C7564D96B174}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Attended family Gathering</t>
+  </si>
+  <si>
+    <t>Prepared for Mid term Examination</t>
   </si>
 </sst>
 </file>
@@ -2228,27 +2231,51 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B31" s="14">
+        <v>600</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>360</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1619DEFF-23F1-492C-B0BF-C7564D96B174}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A096C20F-4661-4AF2-8E37-4BAB65CB0222}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>Prepared for Mid term Examination</t>
+  </si>
+  <si>
+    <t>Classes were canceled so utilized the day to study for mid term</t>
   </si>
 </sst>
 </file>
@@ -2277,27 +2280,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B32" s="14">
+        <v>430</v>
+      </c>
+      <c r="C32" s="14">
+        <v>120</v>
+      </c>
+      <c r="D32" s="14">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>360</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A096C20F-4661-4AF2-8E37-4BAB65CB0222}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E916778A-4CF6-4975-9E2F-B70DB0592DE0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="83">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Classes were canceled so utilized the day to study for mid term</t>
+  </si>
+  <si>
+    <t>Attended a family event</t>
   </si>
 </sst>
 </file>
@@ -2327,70 +2330,142 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B33" s="14">
+        <v>540</v>
+      </c>
+      <c r="C33" s="14">
+        <v>120</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B34" s="14">
+        <v>610</v>
+      </c>
+      <c r="C34" s="14">
+        <v>120</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>360</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B35" s="14">
+        <v>570</v>
+      </c>
+      <c r="C35" s="14">
+        <v>120</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>420</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E916778A-4CF6-4975-9E2F-B70DB0592DE0}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9D0C0A-F66F-41A4-88EF-63CEEDA420B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="84">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Attended a family event</t>
+  </si>
+  <si>
+    <t>Mid term preparation</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2332,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
         <v>46294</v>
       </c>
@@ -2468,26 +2471,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B36" s="14">
+        <v>540</v>
+      </c>
+      <c r="C36" s="14">
+        <v>120</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>300</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9D0C0A-F66F-41A4-88EF-63CEEDA420B9}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25818AC2-B727-4A37-8536-32CC1226D5B1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="84">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -2517,26 +2517,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B37" s="14">
+        <v>540</v>
+      </c>
+      <c r="C37" s="14">
+        <v>180</v>
+      </c>
+      <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>240</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{9EF3589A-8A8C-4C6C-8712-BA5655E0F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25818AC2-B727-4A37-8536-32CC1226D5B1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8727418-3E6C-4740-8B8D-A20CB225513B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="85">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Mid term preparation</t>
+  </si>
+  <si>
+    <t>Was not feeling well today</t>
   </si>
 </sst>
 </file>
@@ -594,10 +597,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2521,7 +2520,7 @@
         <v>46298</v>
       </c>
       <c r="B37" s="14">
-        <v>540</v>
+        <v>480</v>
       </c>
       <c r="C37" s="14">
         <v>180</v>
@@ -2543,11 +2542,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>62</v>
@@ -2563,26 +2562,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B38" s="14">
+        <v>660</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>120</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8727418-3E6C-4740-8B8D-A20CB225513B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="86">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Was not feeling well today</t>
+  </si>
+  <si>
+    <t>Attended online classes and practiced for mid term</t>
   </si>
 </sst>
 </file>
@@ -2607,27 +2610,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B39" s="14">
+        <v>580</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>420</v>
+      </c>
+      <c r="G39" s="14">
+        <v>7</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA308538-74EA-41E7-AECC-BBDDC49FC93E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="87">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Attended online classes and practiced for mid term</t>
+  </si>
+  <si>
+    <t>Attended online classes and worked on project</t>
   </si>
 </sst>
 </file>
@@ -2656,27 +2659,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B40" s="14">
+        <v>500</v>
+      </c>
+      <c r="C40" s="14">
+        <v>120</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>180</v>
+      </c>
+      <c r="G40" s="14">
+        <v>3</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA308538-74EA-41E7-AECC-BBDDC49FC93E}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2518E0C1-99BE-4EA8-A0EF-1C9C27372F0A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="89">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>Attended online classes and worked on project</t>
+  </si>
+  <si>
+    <t>Went for Shopping</t>
+  </si>
+  <si>
+    <t>Utilized my time in hobby and mid term preperation</t>
   </si>
 </sst>
 </file>
@@ -603,6 +609,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2705,49 +2715,97 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B41" s="14">
+        <v>560</v>
+      </c>
+      <c r="C41" s="14">
+        <v>120</v>
+      </c>
+      <c r="D41" s="14">
+        <v>240</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>300</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B42" s="14">
+        <v>540</v>
+      </c>
+      <c r="C42" s="14">
+        <v>120</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="14">
+        <v>0</v>
+      </c>
+      <c r="H42" s="14">
+        <v>420</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2518E0C1-99BE-4EA8-A0EF-1C9C27372F0A}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE98FC6-A136-4855-A968-EBB0A1D05ABF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="89">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -2808,26 +2808,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B43" s="14">
+        <v>680</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>240</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{EBB6901B-665F-41B4-BBB2-98A94D0A499C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FE98FC6-A136-4855-A968-EBB0A1D05ABF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Utilized my time in hobby and mid term preperation</t>
+  </si>
+  <si>
+    <t>Celebrated birthday</t>
   </si>
 </sst>
 </file>
@@ -609,10 +612,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2853,49 +2852,97 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B44" s="14">
+        <v>460</v>
+      </c>
+      <c r="C44" s="14">
+        <v>180</v>
+      </c>
+      <c r="D44" s="14">
+        <v>240</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>180</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B45" s="14">
+        <v>600</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>420</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\ドキュメント\CAP776\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90394E9B-E82D-4FED-8390-EA4B375DC9A9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="91">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>Celebrated birthday</t>
+  </si>
+  <si>
+    <t>Was having Mid term exam and prepared for next exam</t>
   </si>
 </sst>
 </file>
@@ -2944,49 +2947,97 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>120</v>
+      </c>
+      <c r="D46" s="14">
+        <v>300</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>420</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+        <v>180</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B47" s="14">
+        <v>570</v>
+      </c>
+      <c r="C47" s="14">
+        <v>120</v>
+      </c>
+      <c r="D47" s="14">
+        <v>240</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>360</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90394E9B-E82D-4FED-8390-EA4B375DC9A9}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA4B9898-ECAF-4B2E-AA0C-6ED0AB5C02D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="93">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -305,6 +305,12 @@
   </si>
   <si>
     <t>Was having Mid term exam and prepared for next exam</t>
+  </si>
+  <si>
+    <t>Was having a day off between exam</t>
+  </si>
+  <si>
+    <t>Was having analytical skills exam</t>
   </si>
 </sst>
 </file>
@@ -615,6 +621,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3040,70 +3050,140 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B48" s="14">
+        <v>620</v>
+      </c>
+      <c r="C48" s="14">
+        <v>120</v>
+      </c>
+      <c r="D48" s="14">
+        <v>180</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>300</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>27</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+    <row r="49" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B49" s="14">
+        <v>600</v>
+      </c>
+      <c r="C49" s="14">
+        <v>120</v>
+      </c>
+      <c r="D49" s="14">
+        <v>300</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>240</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B50" s="14">
+        <v>510</v>
+      </c>
+      <c r="C50" s="14">
+        <v>120</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>360</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA4B9898-ECAF-4B2E-AA0C-6ED0AB5C02D0}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E3C080-D128-45B2-912D-492464BA1985}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="96">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>Was having analytical skills exam</t>
+  </si>
+  <si>
+    <t>Attended all classes</t>
+  </si>
+  <si>
+    <t>Was having last exam</t>
+  </si>
+  <si>
+    <t>Having a day off after classes</t>
   </si>
 </sst>
 </file>
@@ -3186,92 +3195,188 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B51" s="14">
+        <v>260</v>
+      </c>
+      <c r="C51" s="14">
+        <v>180</v>
+      </c>
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>480</v>
+      </c>
+      <c r="I51" s="15">
+        <f>IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
+        <v>920</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="1"/>
+        <v>520</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B52" s="14">
+        <v>630</v>
+      </c>
+      <c r="C52" s="14">
+        <v>120</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>420</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+        <v>270</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B53" s="14">
+        <v>450</v>
+      </c>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>420</v>
+      </c>
+      <c r="G53" s="14">
+        <v>7</v>
+      </c>
+      <c r="H53" s="14">
+        <v>360</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+        <v>150</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B54" s="14">
+        <v>470</v>
+      </c>
+      <c r="C54" s="14">
+        <v>180</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>360</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79E3C080-D128-45B2-912D-492464BA1985}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65B777BD-C921-4F2B-AA4A-A442A1BC8BC7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="97">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>Having a day off after classes</t>
+  </si>
+  <si>
+    <t>Attended some of the classes and spent rest of the time in working on c++ project</t>
   </si>
 </sst>
 </file>
@@ -3378,27 +3381,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+    <row r="55" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B55" s="14">
+        <v>570</v>
+      </c>
+      <c r="C55" s="14">
+        <v>180</v>
+      </c>
+      <c r="D55" s="14">
+        <v>180</v>
+      </c>
+      <c r="E55" s="14">
+        <v>180</v>
+      </c>
+      <c r="F55" s="14">
+        <v>120</v>
+      </c>
+      <c r="G55" s="14">
+        <v>2</v>
+      </c>
+      <c r="H55" s="14">
+        <v>180</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65B777BD-C921-4F2B-AA4A-A442A1BC8BC7}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E460A13-F8AA-4981-8CFB-150B846D734F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="99">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>Attended some of the classes and spent rest of the time in working on c++ project</t>
+  </si>
+  <si>
+    <t>Attended all the classes</t>
+  </si>
+  <si>
+    <t>Worked on project</t>
   </si>
 </sst>
 </file>
@@ -3329,7 +3335,7 @@
         <v>63</v>
       </c>
       <c r="M53" s="16" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="N53" s="17" t="s">
         <v>93</v>
@@ -3418,7 +3424,7 @@
         <v>26</v>
       </c>
       <c r="L55" s="16" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="M55" s="16" t="s">
         <v>27</v>
@@ -3428,48 +3434,96 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B56" s="14">
+        <v>420</v>
+      </c>
+      <c r="C56" s="14">
+        <v>180</v>
+      </c>
+      <c r="D56" s="14">
+        <v>240</v>
+      </c>
+      <c r="E56" s="14">
+        <v>120</v>
+      </c>
+      <c r="F56" s="14">
+        <v>180</v>
+      </c>
+      <c r="G56" s="14">
+        <v>3</v>
+      </c>
+      <c r="H56" s="14">
+        <v>240</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B57" s="14">
+        <v>450</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>180</v>
+      </c>
+      <c r="F57" s="14">
+        <v>360</v>
+      </c>
+      <c r="G57" s="14">
+        <v>6</v>
+      </c>
+      <c r="H57" s="14">
+        <v>180</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/data/12614066.xlsx
+++ b/data/12614066.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ff43fa014baa151/ドキュメント/CAP776/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E460A13-F8AA-4981-8CFB-150B846D734F}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{CADF272E-8801-4F55-9852-9CC755460BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD593FD-949E-4C3C-89A8-EFC6658339B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -329,6 +329,18 @@
   </si>
   <si>
     <t>Worked on project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Went for shopping </t>
+  </si>
+  <si>
+    <t>Had family gathering</t>
+  </si>
+  <si>
+    <t>Was not feeling well</t>
+  </si>
+  <si>
+    <t>No classes</t>
   </si>
 </sst>
 </file>
@@ -3525,159 +3537,327 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B58" s="14">
+        <v>510</v>
+      </c>
+      <c r="C58" s="14">
+        <v>120</v>
+      </c>
+      <c r="D58" s="14">
+        <v>240</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>360</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B59" s="14">
+        <v>470</v>
+      </c>
+      <c r="C59" s="14">
+        <v>120</v>
+      </c>
+      <c r="D59" s="14">
+        <v>180</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>180</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B60" s="14">
+        <v>560</v>
+      </c>
+      <c r="C60" s="14">
+        <v>120</v>
+      </c>
+      <c r="D60" s="14">
+        <v>180</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>360</v>
+      </c>
+      <c r="G60" s="14">
+        <v>6</v>
+      </c>
+      <c r="H60" s="14">
+        <v>180</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B61" s="14">
+        <v>300</v>
+      </c>
+      <c r="C61" s="14">
+        <v>120</v>
+      </c>
+      <c r="D61" s="14">
+        <v>120</v>
+      </c>
+      <c r="E61" s="14">
+        <v>120</v>
+      </c>
+      <c r="F61" s="14">
+        <v>60</v>
+      </c>
+      <c r="G61" s="14">
+        <v>1</v>
+      </c>
+      <c r="H61" s="14">
+        <v>480</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B62" s="14">
+        <v>510</v>
+      </c>
+      <c r="C62" s="14">
+        <v>120</v>
+      </c>
+      <c r="D62" s="14">
+        <v>120</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>240</v>
+      </c>
+      <c r="G62" s="14">
+        <v>4</v>
+      </c>
+      <c r="H62" s="14">
+        <v>0</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" ref="I62:I125" si="2">IF(SUM(B62:F62,H62)=0,"",SUM(B62:F62,H62))</f>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" ref="J62:J125" si="3">IF(I62="","",1440-I62)</f>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B63" s="14">
+        <v>460</v>
+      </c>
+      <c r="C63" s="14">
+        <v>120</v>
+      </c>
+      <c r="D63" s="14">
+        <v>120</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>0</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B64" s="14">
+        <v>440</v>
+      </c>
+      <c r="C64" s="14">
+        <v>120</v>
+      </c>
+      <c r="D64" s="14">
+        <v>60</v>
+      </c>
+      <c r="E64" s="14">
+        <v>120</v>
+      </c>
+      <c r="F64" s="14">
+        <v>120</v>
+      </c>
+      <c r="G64" s="14">
+        <v>2</v>
+      </c>
+      <c r="H64" s="14">
+        <v>240</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>
